--- a/technology_surveys/017_tech_product_user_experience_report_form--technology_surveys.xlsx
+++ b/technology_surveys/017_tech_product_user_experience_report_form--technology_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Product Name</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Category Id</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Page Id</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>User</t>
+          <t>User Id</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>feedback_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Feedback</t>
+          <t>Feedback 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>product_info</t>
+          <t>product_info_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Product Info 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tech</t>
+          <t>Tech (2)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>phone_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Phone 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1101,7 +1101,7 @@
   <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1364,7 +1364,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>product_info_choices</t>
+          <t>product_info_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1381,7 +1381,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>product_info_choices</t>
+          <t>product_info_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
